--- a/Recursos/Recursos-modelo.xlsx
+++ b/Recursos/Recursos-modelo.xlsx
@@ -1176,7 +1176,7 @@
     <t xml:space="preserve">Indústria de embalagens plásticas</t>
   </si>
   <si>
-    <t xml:space="preserve">Supervisor de manutenção, com o gerente de produção</t>
+    <t xml:space="preserve">Supervisor de manutenção, com o gerente industrial</t>
   </si>
   <si>
     <t xml:space="preserve">Três turnos, todos os dias: 744 horas no mês. A impressora trabalha em dois turnos: 496 horas.</t>
@@ -2094,11 +2094,11 @@
         </c:ser>
         <c:gapWidth val="70"/>
         <c:overlap val="0"/>
-        <c:axId val="81788844"/>
-        <c:axId val="65999065"/>
+        <c:axId val="65922747"/>
+        <c:axId val="87911050"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="81788844"/>
+        <c:axId val="65922747"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2130,7 +2130,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65999065"/>
+        <c:crossAx val="87911050"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2138,7 +2138,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="65999065"/>
+        <c:axId val="87911050"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2178,7 +2178,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81788844"/>
+        <c:crossAx val="65922747"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>

--- a/Recursos/Recursos-modelo.xlsx
+++ b/Recursos/Recursos-modelo.xlsx
@@ -22,7 +22,7 @@
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">Ambiente!$B$1:$N$41</definedName>
     <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">Checklist!$B$1:$E$24</definedName>
     <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Area" vbProcedure="false">'Exemplo 1 - Pizzaria'!$B$1:$Q$60</definedName>
-    <definedName function="false" hidden="false" localSheetId="8" name="_xlnm.Print_Area" vbProcedure="false">'Exemplo 2 - Indústria'!$B$1:$Q$61</definedName>
+    <definedName function="false" hidden="false" localSheetId="8" name="_xlnm.Print_Area" vbProcedure="false">'Exemplo 2 - Indústria'!$B$1:$Q$62</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">Infraestrutura!$B$1:$Q$55</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Instruções!$B$1:$C$47</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Manutenções!$B$1:$M$91</definedName>
@@ -187,7 +187,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="417">
   <si>
     <t xml:space="preserve">Recursos, infraestrutura e ambiente — Como usar esta planilha</t>
   </si>
@@ -903,7 +903,7 @@
     <t xml:space="preserve">Gerente da loja, com o pizzaiolo líder</t>
   </si>
   <si>
-    <t xml:space="preserve">Loja aberta das 18h à meia-noite: 180 horas no mês. Câmara fria e sistema ligados o tempo todo.</t>
+    <t xml:space="preserve">Loja aberta das 18h à meia-noite: 180 horas no mês. A câmara fria fica ligada o tempo todo: 720 horas. O sistema de pedidos é contado nas horas de loja aberta.</t>
   </si>
   <si>
     <t xml:space="preserve">Origem</t>
@@ -1044,7 +1044,7 @@
     <t xml:space="preserve">Preventiva</t>
   </si>
   <si>
-    <t xml:space="preserve">Atualização do sistema e cópia de segurança testada.</t>
+    <t xml:space="preserve">Atualização de versão do sistema e cópia de segurança testada.</t>
   </si>
   <si>
     <t xml:space="preserve">Limpeza dos queimadores e teste da válvula de segurança.</t>
@@ -1062,7 +1062,7 @@
     <t xml:space="preserve">Capacitor trocado. Alarme de temperatura instalado, contingência escrita e revisão marcada para 05/05.</t>
   </si>
   <si>
-    <t xml:space="preserve">18 kg de mussarela e molho descartados (RNC 2027-27).</t>
+    <t xml:space="preserve">18 kg de muçarela e molho descartados (registro de produto não conforme 2027-27).</t>
   </si>
   <si>
     <t xml:space="preserve">Sistema fora do ar na sexta, das 20h às 21h30.</t>
@@ -1152,15 +1152,9 @@
     <t xml:space="preserve">Pedidos do sistema divididos pelos pizzaiolos, toda sexta</t>
   </si>
   <si>
-    <t xml:space="preserve">Rever a escala da sexta em maio, com a demanda de abril.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Horas extras por pessoa na semana</t>
   </si>
   <si>
-    <t xml:space="preserve">Social</t>
-  </si>
-  <si>
     <t xml:space="preserve">Loja</t>
   </si>
   <si>
@@ -1182,7 +1176,7 @@
     <t xml:space="preserve">Três turnos, todos os dias: 744 horas no mês. A impressora trabalha em dois turnos: 496 horas.</t>
   </si>
   <si>
-    <t xml:space="preserve">Análise crítica do semestre: as paradas da extrusora 3 foram a segunda causa dos atrasos, e o turno da noite trabalha com gente a menos desde as férias de junho.</t>
+    <t xml:space="preserve">Preparação da análise crítica de 19/08/2027: as paradas da extrusora 3 foram a segunda causa dos atrasos, e o turno da noite trabalha com gente a menos desde as férias de junho.</t>
   </si>
   <si>
     <t xml:space="preserve">Operador de extrusão</t>
@@ -1242,6 +1236,12 @@
     <t xml:space="preserve">Pedidos redistribuídos entre as extrusoras 1 e 2, com hora extra.</t>
   </si>
   <si>
+    <t xml:space="preserve">EXT-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extrusora 4</t>
+  </si>
+  <si>
     <t xml:space="preserve">IMP-01</t>
   </si>
   <si>
@@ -1329,7 +1329,7 @@
     <t xml:space="preserve">Resistência trocada. Preventiva remarcada para 07/08, com os pedidos redistribuídos.</t>
   </si>
   <si>
-    <t xml:space="preserve">Bobina em produção segregada e moída (RNC 2027-29).</t>
+    <t xml:space="preserve">Bobina em produção segregada e moída (registro de produto não conforme 2027-29).</t>
   </si>
   <si>
     <t xml:space="preserve">Anilox entupido: falha na cor.</t>
@@ -1350,7 +1350,7 @@
     <t xml:space="preserve">Rosca recuperada. Medição da rosca antecipada para a preventiva de 07/08.</t>
   </si>
   <si>
-    <t xml:space="preserve">6 bobinas com espessura fora segregadas (RNC 2027-30).</t>
+    <t xml:space="preserve">6 bobinas com espessura fora segregadas (registro de produto não conforme 2027-30).</t>
   </si>
   <si>
     <t xml:space="preserve">Troca das facas e limpeza geral.</t>
@@ -1371,7 +1371,7 @@
     <t xml:space="preserve">Cabo do termopar danificado pela vibração.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cabo trocado e termopar TER-Z3 verificado contra o padrão PAD-01.</t>
+    <t xml:space="preserve">Cabo trocado. Termopar TER-Z3 calibrado no local por laboratório externo, a 190 °C, antes de a extrusora voltar.</t>
   </si>
   <si>
     <t xml:space="preserve">Temperatura do salão de impressão</t>
@@ -1407,7 +1407,7 @@
     <t xml:space="preserve">Medição a cada 6 meses</t>
   </si>
   <si>
-    <t xml:space="preserve">Alarme luminoso instalado nas três extrusoras. Protetor auricular obrigatório.</t>
+    <t xml:space="preserve">Alarme luminoso instalado nas quatro extrusoras. Protetor auricular obrigatório.</t>
   </si>
   <si>
     <t xml:space="preserve">Limpeza da área de rebobinamento</t>
@@ -2094,11 +2094,11 @@
         </c:ser>
         <c:gapWidth val="70"/>
         <c:overlap val="0"/>
-        <c:axId val="65922747"/>
-        <c:axId val="87911050"/>
+        <c:axId val="72058169"/>
+        <c:axId val="12351476"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="65922747"/>
+        <c:axId val="72058169"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2130,7 +2130,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87911050"/>
+        <c:crossAx val="12351476"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2138,7 +2138,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="87911050"/>
+        <c:axId val="12351476"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2178,7 +2178,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65922747"/>
+        <c:crossAx val="72058169"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -11363,15 +11363,13 @@
         <v>20</v>
       </c>
       <c r="M52" s="40" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N52" s="15" t="str">
         <f aca="false">IF(B52="","",IF(M52="","Sem medição",IF(OR(AND(K52&lt;&gt;"",M52&lt;K52),AND(L52&lt;&gt;"",M52&gt;L52)),"Fora","Dentro")))</f>
-        <v>Fora</v>
-      </c>
-      <c r="O52" s="39" t="s">
-        <v>321</v>
-      </c>
+        <v>Dentro</v>
+      </c>
+      <c r="O52" s="39"/>
       <c r="P52" s="39"/>
       <c r="Q52" s="16" t="str">
         <f aca="false">IF(B52="","",IF(F52="","Falta por que afeta o produto",IF(J52="","Falta como é controlado",IF(AND(K52="",L52=""),"Falta o limite",IF(N52="Sem medição","Falta a medição",IF(AND(N52="Fora",O52=""),"Fora do limite: falta a ação","OK"))))))</f>
@@ -11380,25 +11378,25 @@
     </row>
     <row r="53" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="38" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C53" s="38"/>
       <c r="D53" s="43" t="s">
+        <v>317</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="F53" s="39" t="s">
         <v>323</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="F53" s="39" t="s">
-        <v>325</v>
       </c>
       <c r="G53" s="39"/>
       <c r="H53" s="39"/>
       <c r="I53" s="47" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="J53" s="39" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="K53" s="40"/>
       <c r="L53" s="40" t="n">
@@ -11515,7 +11513,7 @@
       <c r="D59" s="18"/>
       <c r="E59" s="19" t="str">
         <f aca="false">COUNTIF(N48:N53,"Dentro")&amp;" dentro"&amp;", "&amp;COUNTIF(N48:N53,"Fora")&amp;" fora"&amp;", "&amp;COUNTIF(N48:N53,"Sem medição")&amp;" sem medição"</f>
-        <v>2 dentro, 3 fora, 1 sem medição</v>
+        <v>3 dentro, 2 fora, 1 sem medição</v>
       </c>
       <c r="F59" s="19"/>
       <c r="G59" s="19"/>
@@ -11758,7 +11756,7 @@
     <tabColor rgb="FF5B6B76"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:Q61"/>
+  <dimension ref="B1:Q62"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -11823,7 +11821,7 @@
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="33" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E4" s="33"/>
       <c r="F4" s="33"/>
@@ -11845,7 +11843,7 @@
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="33" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E5" s="33"/>
       <c r="F5" s="33"/>
@@ -11867,7 +11865,7 @@
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="33" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E6" s="33"/>
       <c r="F6" s="33"/>
@@ -11883,13 +11881,13 @@
       <c r="P6" s="33"/>
       <c r="Q6" s="33"/>
     </row>
-    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
         <v>239</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="33" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E7" s="33"/>
       <c r="F7" s="33"/>
@@ -11994,30 +11992,30 @@
     </row>
     <row r="14" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="38" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C14" s="38"/>
       <c r="D14" s="7" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E14" s="39" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G14" s="40" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="13" t="n">
         <f aca="false">IF(OR(N(F14)=0,N(G14)=0),"",ROUNDUP(F14/G14,0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" s="14" t="n">
         <f aca="false">IF(OR(H14="",I14=""),"",I14-H14)</f>
@@ -12038,30 +12036,30 @@
     </row>
     <row r="15" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="38" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C15" s="38"/>
       <c r="D15" s="7" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E15" s="39" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" s="40" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="13" t="n">
         <f aca="false">IF(OR(N(F15)=0,N(G15)=0),"",ROUNDUP(F15/G15,0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="14" t="n">
         <f aca="false">IF(OR(H15="",I15=""),"",I15-H15)</f>
@@ -12082,30 +12080,30 @@
     </row>
     <row r="16" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="38" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C16" s="38"/>
       <c r="D16" s="7" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E16" s="39" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="40" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="13" t="n">
         <f aca="false">IF(OR(N(F16)=0,N(G16)=0),"",ROUNDUP(F16/G16,0))</f>
+        <v>4</v>
+      </c>
+      <c r="I16" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="I16" s="40" t="n">
-        <v>2</v>
-      </c>
       <c r="J16" s="40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K16" s="14" t="n">
         <f aca="false">IF(OR(H16="",I16=""),"",I16-H16)</f>
@@ -12126,14 +12124,14 @@
     </row>
     <row r="17" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="38" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C17" s="38"/>
       <c r="D17" s="7" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E17" s="39" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F17" s="40" t="n">
         <v>1</v>
@@ -12170,14 +12168,14 @@
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="38" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C18" s="38"/>
       <c r="D18" s="7" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E18" s="39" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F18" s="40" t="n">
         <v>24</v>
@@ -12214,14 +12212,14 @@
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="38" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C19" s="38"/>
       <c r="D19" s="7" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E19" s="39" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F19" s="40" t="n">
         <v>24</v>
@@ -12258,14 +12256,14 @@
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="38" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C20" s="38"/>
       <c r="D20" s="7" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E20" s="39" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F20" s="40" t="n">
         <v>5</v>
@@ -12306,10 +12304,10 @@
       </c>
       <c r="C21" s="38"/>
       <c r="D21" s="7" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E21" s="39" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F21" s="40" t="n">
         <v>4</v>
@@ -12414,16 +12412,16 @@
     </row>
     <row r="25" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="42" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D25" s="39" t="s">
         <v>257</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F25" s="43" t="s">
         <v>258</v>
@@ -12439,7 +12437,7 @@
         <v>46609</v>
       </c>
       <c r="J25" s="39" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="K25" s="40" t="n">
         <v>744</v>
@@ -12449,11 +12447,11 @@
         <v>Em dia</v>
       </c>
       <c r="M25" s="14" t="n">
-        <f aca="false">IF(OR(B25="",$D$8="",$D$9=""),"",COUNTIFS($C$38:$C$45,B25,$D$38:$D$45,"Corretiva",$B$38:$B$45,"&gt;="&amp;$D$8,$B$38:$B$45,"&lt;="&amp;$D$9))</f>
+        <f aca="false">IF(OR(B25="",$D$8="",$D$9=""),"",COUNTIFS($C$39:$C$46,B25,$D$39:$D$46,"Corretiva",$B$39:$B$46,"&gt;="&amp;$D$8,$B$39:$B$46,"&lt;="&amp;$D$9))</f>
         <v>0</v>
       </c>
       <c r="N25" s="25" t="n">
-        <f aca="false">IF(OR(B25="",$D$8="",$D$9=""),"",SUMIFS($E$38:$E$45,$C$38:$C$45,B25,$D$38:$D$45,"Corretiva",$B$38:$B$45,"&gt;="&amp;$D$8,$B$38:$B$45,"&lt;="&amp;$D$9))</f>
+        <f aca="false">IF(OR(B25="",$D$8="",$D$9=""),"",SUMIFS($E$39:$E$46,$C$39:$C$46,B25,$D$39:$D$46,"Corretiva",$B$39:$B$46,"&gt;="&amp;$D$8,$B$39:$B$46,"&lt;="&amp;$D$9))</f>
         <v>0</v>
       </c>
       <c r="O25" s="26" t="n">
@@ -12468,16 +12466,16 @@
     </row>
     <row r="26" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="42" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D26" s="39" t="s">
         <v>257</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F26" s="43" t="s">
         <v>258</v>
@@ -12493,7 +12491,7 @@
         <v>46553</v>
       </c>
       <c r="J26" s="39" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="K26" s="40" t="n">
         <v>744</v>
@@ -12503,11 +12501,11 @@
         <v>Atrasada</v>
       </c>
       <c r="M26" s="14" t="n">
-        <f aca="false">IF(OR(B26="",$D$8="",$D$9=""),"",COUNTIFS($C$38:$C$45,B26,$D$38:$D$45,"Corretiva",$B$38:$B$45,"&gt;="&amp;$D$8,$B$38:$B$45,"&lt;="&amp;$D$9))</f>
+        <f aca="false">IF(OR(B26="",$D$8="",$D$9=""),"",COUNTIFS($C$39:$C$46,B26,$D$39:$D$46,"Corretiva",$B$39:$B$46,"&gt;="&amp;$D$8,$B$39:$B$46,"&lt;="&amp;$D$9))</f>
         <v>3</v>
       </c>
       <c r="N26" s="25" t="n">
-        <f aca="false">IF(OR(B26="",$D$8="",$D$9=""),"",SUMIFS($E$38:$E$45,$C$38:$C$45,B26,$D$38:$D$45,"Corretiva",$B$38:$B$45,"&gt;="&amp;$D$8,$B$38:$B$45,"&lt;="&amp;$D$9))</f>
+        <f aca="false">IF(OR(B26="",$D$8="",$D$9=""),"",SUMIFS($E$39:$E$46,$C$39:$C$46,B26,$D$39:$D$46,"Corretiva",$B$39:$B$46,"&gt;="&amp;$D$8,$B$39:$B$46,"&lt;="&amp;$D$9))</f>
         <v>40</v>
       </c>
       <c r="O26" s="26" t="n">
@@ -12522,51 +12520,51 @@
     </row>
     <row r="27" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="42" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D27" s="39" t="s">
         <v>257</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="F27" s="43" t="s">
         <v>258</v>
       </c>
       <c r="G27" s="43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H27" s="44" t="n">
-        <v>46588</v>
+        <v>46559</v>
       </c>
       <c r="I27" s="24" t="n">
         <f aca="false">IF(OR(H27="",G27=""),"",EDATE(H27,G27))</f>
-        <v>46619</v>
+        <v>46651</v>
       </c>
       <c r="J27" s="39" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="K27" s="40" t="n">
-        <v>496</v>
+        <v>744</v>
       </c>
       <c r="L27" s="15" t="str">
         <f aca="false">IF(B27="","",IF(G27="","Sem plano",IF(H27="","Atrasada",IF(AND(ISNUMBER($D$9),I27&lt;$D$9),"Atrasada",IF(AND(ISNUMBER($D$9),I27-$D$9&lt;=7),"Vence em 7 dias","Em dia")))))</f>
         <v>Em dia</v>
       </c>
       <c r="M27" s="14" t="n">
-        <f aca="false">IF(OR(B27="",$D$8="",$D$9=""),"",COUNTIFS($C$38:$C$45,B27,$D$38:$D$45,"Corretiva",$B$38:$B$45,"&gt;="&amp;$D$8,$B$38:$B$45,"&lt;="&amp;$D$9))</f>
-        <v>1</v>
+        <f aca="false">IF(OR(B27="",$D$8="",$D$9=""),"",COUNTIFS($C$39:$C$46,B27,$D$39:$D$46,"Corretiva",$B$39:$B$46,"&gt;="&amp;$D$8,$B$39:$B$46,"&lt;="&amp;$D$9))</f>
+        <v>0</v>
       </c>
       <c r="N27" s="25" t="n">
-        <f aca="false">IF(OR(B27="",$D$8="",$D$9=""),"",SUMIFS($E$38:$E$45,$C$38:$C$45,B27,$D$38:$D$45,"Corretiva",$B$38:$B$45,"&gt;="&amp;$D$8,$B$38:$B$45,"&lt;="&amp;$D$9))</f>
-        <v>4</v>
+        <f aca="false">IF(OR(B27="",$D$8="",$D$9=""),"",SUMIFS($E$39:$E$46,$C$39:$C$46,B27,$D$39:$D$46,"Corretiva",$B$39:$B$46,"&gt;="&amp;$D$8,$B$39:$B$46,"&lt;="&amp;$D$9))</f>
+        <v>0</v>
       </c>
       <c r="O27" s="26" t="n">
         <f aca="false">IF(OR(N(K27)=0,N27=""),"",(K27-N27)/K27)</f>
-        <v>0.991935483870968</v>
+        <v>1</v>
       </c>
       <c r="P27" s="16" t="str">
         <f aca="false">IF(B27="","",IF(D27="","Falta o tipo",IF(F27="","Falta a criticidade",IF(AND(OR(F27="Alta",F27="Média"),G27=""),"Sem plano de preventiva",IF(L27="Atrasada","Preventiva atrasada",IF(AND(F27="Alta",J27=""),"Crítico sem contingência",IF(AND(ISNUMBER(O27),ISNUMBER($D$10)),IF(O27&lt;$D$10-0.000000001,"Disponibilidade abaixo da meta","OK"),"OK")))))))</f>
@@ -12574,51 +12572,53 @@
       </c>
       <c r="Q27" s="16"/>
     </row>
-    <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="42" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C28" s="38" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D28" s="39" t="s">
         <v>257</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="F28" s="43" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="G28" s="43" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H28" s="44" t="n">
-        <v>46438</v>
+        <v>46588</v>
       </c>
       <c r="I28" s="24" t="n">
         <f aca="false">IF(OR(H28="",G28=""),"",EDATE(H28,G28))</f>
         <v>46619</v>
       </c>
-      <c r="J28" s="39"/>
+      <c r="J28" s="39" t="s">
+        <v>354</v>
+      </c>
       <c r="K28" s="40" t="n">
-        <v>744</v>
+        <v>496</v>
       </c>
       <c r="L28" s="15" t="str">
         <f aca="false">IF(B28="","",IF(G28="","Sem plano",IF(H28="","Atrasada",IF(AND(ISNUMBER($D$9),I28&lt;$D$9),"Atrasada",IF(AND(ISNUMBER($D$9),I28-$D$9&lt;=7),"Vence em 7 dias","Em dia")))))</f>
         <v>Em dia</v>
       </c>
       <c r="M28" s="14" t="n">
-        <f aca="false">IF(OR(B28="",$D$8="",$D$9=""),"",COUNTIFS($C$38:$C$45,B28,$D$38:$D$45,"Corretiva",$B$38:$B$45,"&gt;="&amp;$D$8,$B$38:$B$45,"&lt;="&amp;$D$9))</f>
-        <v>0</v>
+        <f aca="false">IF(OR(B28="",$D$8="",$D$9=""),"",COUNTIFS($C$39:$C$46,B28,$D$39:$D$46,"Corretiva",$B$39:$B$46,"&gt;="&amp;$D$8,$B$39:$B$46,"&lt;="&amp;$D$9))</f>
+        <v>1</v>
       </c>
       <c r="N28" s="25" t="n">
-        <f aca="false">IF(OR(B28="",$D$8="",$D$9=""),"",SUMIFS($E$38:$E$45,$C$38:$C$45,B28,$D$38:$D$45,"Corretiva",$B$38:$B$45,"&gt;="&amp;$D$8,$B$38:$B$45,"&lt;="&amp;$D$9))</f>
-        <v>0</v>
+        <f aca="false">IF(OR(B28="",$D$8="",$D$9=""),"",SUMIFS($E$39:$E$46,$C$39:$C$46,B28,$D$39:$D$46,"Corretiva",$B$39:$B$46,"&gt;="&amp;$D$8,$B$39:$B$46,"&lt;="&amp;$D$9))</f>
+        <v>4</v>
       </c>
       <c r="O28" s="26" t="n">
         <f aca="false">IF(OR(N(K28)=0,N28=""),"",(K28-N28)/K28)</f>
-        <v>1</v>
+        <v>0.991935483870968</v>
       </c>
       <c r="P28" s="16" t="str">
         <f aca="false">IF(B28="","",IF(D28="","Falta o tipo",IF(F28="","Falta a criticidade",IF(AND(OR(F28="Alta",F28="Média"),G28=""),"Sem plano de preventiva",IF(L28="Atrasada","Preventiva atrasada",IF(AND(F28="Alta",J28=""),"Crítico sem contingência",IF(AND(ISNUMBER(O28),ISNUMBER($D$10)),IF(O28&lt;$D$10-0.000000001,"Disponibilidade abaixo da meta","OK"),"OK")))))))</f>
@@ -12628,29 +12628,29 @@
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="42" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="D29" s="39" t="s">
         <v>257</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="F29" s="43" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="G29" s="43" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H29" s="44" t="n">
-        <v>46540</v>
+        <v>46438</v>
       </c>
       <c r="I29" s="24" t="n">
         <f aca="false">IF(OR(H29="",G29=""),"",EDATE(H29,G29))</f>
-        <v>46632</v>
+        <v>46619</v>
       </c>
       <c r="J29" s="39"/>
       <c r="K29" s="40" t="n">
@@ -12661,11 +12661,11 @@
         <v>Em dia</v>
       </c>
       <c r="M29" s="14" t="n">
-        <f aca="false">IF(OR(B29="",$D$8="",$D$9=""),"",COUNTIFS($C$38:$C$45,B29,$D$38:$D$45,"Corretiva",$B$38:$B$45,"&gt;="&amp;$D$8,$B$38:$B$45,"&lt;="&amp;$D$9))</f>
+        <f aca="false">IF(OR(B29="",$D$8="",$D$9=""),"",COUNTIFS($C$39:$C$46,B29,$D$39:$D$46,"Corretiva",$B$39:$B$46,"&gt;="&amp;$D$8,$B$39:$B$46,"&lt;="&amp;$D$9))</f>
         <v>0</v>
       </c>
       <c r="N29" s="25" t="n">
-        <f aca="false">IF(OR(B29="",$D$8="",$D$9=""),"",SUMIFS($E$38:$E$45,$C$38:$C$45,B29,$D$38:$D$45,"Corretiva",$B$38:$B$45,"&gt;="&amp;$D$8,$B$38:$B$45,"&lt;="&amp;$D$9))</f>
+        <f aca="false">IF(OR(B29="",$D$8="",$D$9=""),"",SUMIFS($E$39:$E$46,$C$39:$C$46,B29,$D$39:$D$46,"Corretiva",$B$39:$B$46,"&gt;="&amp;$D$8,$B$39:$B$46,"&lt;="&amp;$D$9))</f>
         <v>0</v>
       </c>
       <c r="O29" s="26" t="n">
@@ -12674,16 +12674,16 @@
       </c>
       <c r="P29" s="16" t="str">
         <f aca="false">IF(B29="","",IF(D29="","Falta o tipo",IF(F29="","Falta a criticidade",IF(AND(OR(F29="Alta",F29="Média"),G29=""),"Sem plano de preventiva",IF(L29="Atrasada","Preventiva atrasada",IF(AND(F29="Alta",J29=""),"Crítico sem contingência",IF(AND(ISNUMBER(O29),ISNUMBER($D$10)),IF(O29&lt;$D$10-0.000000001,"Disponibilidade abaixo da meta","OK"),"OK")))))))</f>
-        <v>Crítico sem contingência</v>
+        <v>OK</v>
       </c>
       <c r="Q29" s="16"/>
     </row>
-    <row r="30" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="42" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C30" s="38" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="D30" s="39" t="s">
         <v>257</v>
@@ -12695,18 +12695,16 @@
         <v>258</v>
       </c>
       <c r="G30" s="43" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H30" s="44" t="n">
-        <v>46487</v>
+        <v>46540</v>
       </c>
       <c r="I30" s="24" t="n">
         <f aca="false">IF(OR(H30="",G30=""),"",EDATE(H30,G30))</f>
-        <v>46670</v>
-      </c>
-      <c r="J30" s="39" t="s">
-        <v>363</v>
-      </c>
+        <v>46632</v>
+      </c>
+      <c r="J30" s="39"/>
       <c r="K30" s="40" t="n">
         <v>744</v>
       </c>
@@ -12715,68 +12713,70 @@
         <v>Em dia</v>
       </c>
       <c r="M30" s="14" t="n">
-        <f aca="false">IF(OR(B30="",$D$8="",$D$9=""),"",COUNTIFS($C$38:$C$45,B30,$D$38:$D$45,"Corretiva",$B$38:$B$45,"&gt;="&amp;$D$8,$B$38:$B$45,"&lt;="&amp;$D$9))</f>
-        <v>1</v>
+        <f aca="false">IF(OR(B30="",$D$8="",$D$9=""),"",COUNTIFS($C$39:$C$46,B30,$D$39:$D$46,"Corretiva",$B$39:$B$46,"&gt;="&amp;$D$8,$B$39:$B$46,"&lt;="&amp;$D$9))</f>
+        <v>0</v>
       </c>
       <c r="N30" s="25" t="n">
-        <f aca="false">IF(OR(B30="",$D$8="",$D$9=""),"",SUMIFS($E$38:$E$45,$C$38:$C$45,B30,$D$38:$D$45,"Corretiva",$B$38:$B$45,"&gt;="&amp;$D$8,$B$38:$B$45,"&lt;="&amp;$D$9))</f>
-        <v>8</v>
+        <f aca="false">IF(OR(B30="",$D$8="",$D$9=""),"",SUMIFS($E$39:$E$46,$C$39:$C$46,B30,$D$39:$D$46,"Corretiva",$B$39:$B$46,"&gt;="&amp;$D$8,$B$39:$B$46,"&lt;="&amp;$D$9))</f>
+        <v>0</v>
       </c>
       <c r="O30" s="26" t="n">
         <f aca="false">IF(OR(N(K30)=0,N30=""),"",(K30-N30)/K30)</f>
-        <v>0.989247311827957</v>
+        <v>1</v>
       </c>
       <c r="P30" s="16" t="str">
         <f aca="false">IF(B30="","",IF(D30="","Falta o tipo",IF(F30="","Falta a criticidade",IF(AND(OR(F30="Alta",F30="Média"),G30=""),"Sem plano de preventiva",IF(L30="Atrasada","Preventiva atrasada",IF(AND(F30="Alta",J30=""),"Crítico sem contingência",IF(AND(ISNUMBER(O30),ISNUMBER($D$10)),IF(O30&lt;$D$10-0.000000001,"Disponibilidade abaixo da meta","OK"),"OK")))))))</f>
-        <v>OK</v>
+        <v>Crítico sem contingência</v>
       </c>
       <c r="Q30" s="16"/>
     </row>
-    <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="42" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C31" s="38" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="D31" s="39" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>249</v>
+        <v>360</v>
       </c>
       <c r="F31" s="43" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="G31" s="43" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H31" s="44" t="n">
-        <v>46512</v>
+        <v>46487</v>
       </c>
       <c r="I31" s="24" t="n">
         <f aca="false">IF(OR(H31="",G31=""),"",EDATE(H31,G31))</f>
-        <v>46604</v>
-      </c>
-      <c r="J31" s="39"/>
+        <v>46670</v>
+      </c>
+      <c r="J31" s="39" t="s">
+        <v>363</v>
+      </c>
       <c r="K31" s="40" t="n">
         <v>744</v>
       </c>
       <c r="L31" s="15" t="str">
         <f aca="false">IF(B31="","",IF(G31="","Sem plano",IF(H31="","Atrasada",IF(AND(ISNUMBER($D$9),I31&lt;$D$9),"Atrasada",IF(AND(ISNUMBER($D$9),I31-$D$9&lt;=7),"Vence em 7 dias","Em dia")))))</f>
-        <v>Vence em 7 dias</v>
+        <v>Em dia</v>
       </c>
       <c r="M31" s="14" t="n">
-        <f aca="false">IF(OR(B31="",$D$8="",$D$9=""),"",COUNTIFS($C$38:$C$45,B31,$D$38:$D$45,"Corretiva",$B$38:$B$45,"&gt;="&amp;$D$8,$B$38:$B$45,"&lt;="&amp;$D$9))</f>
-        <v>0</v>
+        <f aca="false">IF(OR(B31="",$D$8="",$D$9=""),"",COUNTIFS($C$39:$C$46,B31,$D$39:$D$46,"Corretiva",$B$39:$B$46,"&gt;="&amp;$D$8,$B$39:$B$46,"&lt;="&amp;$D$9))</f>
+        <v>1</v>
       </c>
       <c r="N31" s="25" t="n">
-        <f aca="false">IF(OR(B31="",$D$8="",$D$9=""),"",SUMIFS($E$38:$E$45,$C$38:$C$45,B31,$D$38:$D$45,"Corretiva",$B$38:$B$45,"&gt;="&amp;$D$8,$B$38:$B$45,"&lt;="&amp;$D$9))</f>
-        <v>0</v>
+        <f aca="false">IF(OR(B31="",$D$8="",$D$9=""),"",SUMIFS($E$39:$E$46,$C$39:$C$46,B31,$D$39:$D$46,"Corretiva",$B$39:$B$46,"&gt;="&amp;$D$8,$B$39:$B$46,"&lt;="&amp;$D$9))</f>
+        <v>8</v>
       </c>
       <c r="O31" s="26" t="n">
         <f aca="false">IF(OR(N(K31)=0,N31=""),"",(K31-N31)/K31)</f>
-        <v>1</v>
+        <v>0.989247311827957</v>
       </c>
       <c r="P31" s="16" t="str">
         <f aca="false">IF(B31="","",IF(D31="","Falta o tipo",IF(F31="","Falta a criticidade",IF(AND(OR(F31="Alta",F31="Média"),G31=""),"Sem plano de preventiva",IF(L31="Atrasada","Preventiva atrasada",IF(AND(F31="Alta",J31=""),"Crítico sem contingência",IF(AND(ISNUMBER(O31),ISNUMBER($D$10)),IF(O31&lt;$D$10-0.000000001,"Disponibilidade abaixo da meta","OK"),"OK")))))))</f>
@@ -12784,51 +12784,51 @@
       </c>
       <c r="Q31" s="16"/>
     </row>
-    <row r="32" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="42" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C32" s="38" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D32" s="39" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>368</v>
+        <v>249</v>
       </c>
       <c r="F32" s="43" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="G32" s="43" t="n">
         <v>3</v>
       </c>
       <c r="H32" s="44" t="n">
-        <v>46571</v>
+        <v>46512</v>
       </c>
       <c r="I32" s="24" t="n">
         <f aca="false">IF(OR(H32="",G32=""),"",EDATE(H32,G32))</f>
-        <v>46663</v>
-      </c>
-      <c r="J32" s="39" t="s">
-        <v>369</v>
-      </c>
-      <c r="K32" s="40"/>
+        <v>46604</v>
+      </c>
+      <c r="J32" s="39"/>
+      <c r="K32" s="40" t="n">
+        <v>744</v>
+      </c>
       <c r="L32" s="15" t="str">
         <f aca="false">IF(B32="","",IF(G32="","Sem plano",IF(H32="","Atrasada",IF(AND(ISNUMBER($D$9),I32&lt;$D$9),"Atrasada",IF(AND(ISNUMBER($D$9),I32-$D$9&lt;=7),"Vence em 7 dias","Em dia")))))</f>
-        <v>Em dia</v>
+        <v>Vence em 7 dias</v>
       </c>
       <c r="M32" s="14" t="n">
-        <f aca="false">IF(OR(B32="",$D$8="",$D$9=""),"",COUNTIFS($C$38:$C$45,B32,$D$38:$D$45,"Corretiva",$B$38:$B$45,"&gt;="&amp;$D$8,$B$38:$B$45,"&lt;="&amp;$D$9))</f>
+        <f aca="false">IF(OR(B32="",$D$8="",$D$9=""),"",COUNTIFS($C$39:$C$46,B32,$D$39:$D$46,"Corretiva",$B$39:$B$46,"&gt;="&amp;$D$8,$B$39:$B$46,"&lt;="&amp;$D$9))</f>
         <v>0</v>
       </c>
       <c r="N32" s="25" t="n">
-        <f aca="false">IF(OR(B32="",$D$8="",$D$9=""),"",SUMIFS($E$38:$E$45,$C$38:$C$45,B32,$D$38:$D$45,"Corretiva",$B$38:$B$45,"&gt;="&amp;$D$8,$B$38:$B$45,"&lt;="&amp;$D$9))</f>
+        <f aca="false">IF(OR(B32="",$D$8="",$D$9=""),"",SUMIFS($E$39:$E$46,$C$39:$C$46,B32,$D$39:$D$46,"Corretiva",$B$39:$B$46,"&gt;="&amp;$D$8,$B$39:$B$46,"&lt;="&amp;$D$9))</f>
         <v>0</v>
       </c>
-      <c r="O32" s="26" t="str">
+      <c r="O32" s="26" t="n">
         <f aca="false">IF(OR(N(K32)=0,N32=""),"",(K32-N32)/K32)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="P32" s="16" t="str">
         <f aca="false">IF(B32="","",IF(D32="","Falta o tipo",IF(F32="","Falta a criticidade",IF(AND(OR(F32="Alta",F32="Média"),G32=""),"Sem plano de preventiva",IF(L32="Atrasada","Preventiva atrasada",IF(AND(F32="Alta",J32=""),"Crítico sem contingência",IF(AND(ISNUMBER(O32),ISNUMBER($D$10)),IF(O32&lt;$D$10-0.000000001,"Disponibilidade abaixo da meta","OK"),"OK")))))))</f>
@@ -12838,49 +12838,49 @@
     </row>
     <row r="33" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="42" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C33" s="38" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="D33" s="39" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="F33" s="43" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="G33" s="43" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H33" s="44" t="n">
-        <v>46280</v>
+        <v>46571</v>
       </c>
       <c r="I33" s="24" t="n">
         <f aca="false">IF(OR(H33="",G33=""),"",EDATE(H33,G33))</f>
-        <v>46645</v>
-      </c>
-      <c r="J33" s="39"/>
-      <c r="K33" s="40" t="n">
-        <v>496</v>
-      </c>
+        <v>46663</v>
+      </c>
+      <c r="J33" s="39" t="s">
+        <v>369</v>
+      </c>
+      <c r="K33" s="40"/>
       <c r="L33" s="15" t="str">
         <f aca="false">IF(B33="","",IF(G33="","Sem plano",IF(H33="","Atrasada",IF(AND(ISNUMBER($D$9),I33&lt;$D$9),"Atrasada",IF(AND(ISNUMBER($D$9),I33-$D$9&lt;=7),"Vence em 7 dias","Em dia")))))</f>
         <v>Em dia</v>
       </c>
       <c r="M33" s="14" t="n">
-        <f aca="false">IF(OR(B33="",$D$8="",$D$9=""),"",COUNTIFS($C$38:$C$45,B33,$D$38:$D$45,"Corretiva",$B$38:$B$45,"&gt;="&amp;$D$8,$B$38:$B$45,"&lt;="&amp;$D$9))</f>
+        <f aca="false">IF(OR(B33="",$D$8="",$D$9=""),"",COUNTIFS($C$39:$C$46,B33,$D$39:$D$46,"Corretiva",$B$39:$B$46,"&gt;="&amp;$D$8,$B$39:$B$46,"&lt;="&amp;$D$9))</f>
         <v>0</v>
       </c>
       <c r="N33" s="25" t="n">
-        <f aca="false">IF(OR(B33="",$D$8="",$D$9=""),"",SUMIFS($E$38:$E$45,$C$38:$C$45,B33,$D$38:$D$45,"Corretiva",$B$38:$B$45,"&gt;="&amp;$D$8,$B$38:$B$45,"&lt;="&amp;$D$9))</f>
+        <f aca="false">IF(OR(B33="",$D$8="",$D$9=""),"",SUMIFS($E$39:$E$46,$C$39:$C$46,B33,$D$39:$D$46,"Corretiva",$B$39:$B$46,"&gt;="&amp;$D$8,$B$39:$B$46,"&lt;="&amp;$D$9))</f>
         <v>0</v>
       </c>
-      <c r="O33" s="26" t="n">
+      <c r="O33" s="26" t="str">
         <f aca="false">IF(OR(N(K33)=0,N33=""),"",(K33-N33)/K33)</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="P33" s="16" t="str">
         <f aca="false">IF(B33="","",IF(D33="","Falta o tipo",IF(F33="","Falta a criticidade",IF(AND(OR(F33="Alta",F33="Média"),G33=""),"Sem plano de preventiva",IF(L33="Atrasada","Preventiva atrasada",IF(AND(F33="Alta",J33=""),"Crítico sem contingência",IF(AND(ISNUMBER(O33),ISNUMBER($D$10)),IF(O33&lt;$D$10-0.000000001,"Disponibilidade abaixo da meta","OK"),"OK")))))))</f>
@@ -12888,45 +12888,51 @@
       </c>
       <c r="Q33" s="16"/>
     </row>
-    <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="42" t="s">
-        <v>281</v>
+        <v>370</v>
       </c>
       <c r="C34" s="38" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D34" s="39" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>249</v>
+        <v>353</v>
       </c>
       <c r="F34" s="43" t="s">
-        <v>283</v>
-      </c>
-      <c r="G34" s="43"/>
-      <c r="H34" s="44"/>
-      <c r="I34" s="24" t="str">
+        <v>267</v>
+      </c>
+      <c r="G34" s="43" t="n">
+        <v>12</v>
+      </c>
+      <c r="H34" s="44" t="n">
+        <v>46280</v>
+      </c>
+      <c r="I34" s="24" t="n">
         <f aca="false">IF(OR(H34="",G34=""),"",EDATE(H34,G34))</f>
-        <v/>
+        <v>46645</v>
       </c>
       <c r="J34" s="39"/>
-      <c r="K34" s="40"/>
+      <c r="K34" s="40" t="n">
+        <v>496</v>
+      </c>
       <c r="L34" s="15" t="str">
         <f aca="false">IF(B34="","",IF(G34="","Sem plano",IF(H34="","Atrasada",IF(AND(ISNUMBER($D$9),I34&lt;$D$9),"Atrasada",IF(AND(ISNUMBER($D$9),I34-$D$9&lt;=7),"Vence em 7 dias","Em dia")))))</f>
-        <v>Sem plano</v>
+        <v>Em dia</v>
       </c>
       <c r="M34" s="14" t="n">
-        <f aca="false">IF(OR(B34="",$D$8="",$D$9=""),"",COUNTIFS($C$38:$C$45,B34,$D$38:$D$45,"Corretiva",$B$38:$B$45,"&gt;="&amp;$D$8,$B$38:$B$45,"&lt;="&amp;$D$9))</f>
+        <f aca="false">IF(OR(B34="",$D$8="",$D$9=""),"",COUNTIFS($C$39:$C$46,B34,$D$39:$D$46,"Corretiva",$B$39:$B$46,"&gt;="&amp;$D$8,$B$39:$B$46,"&lt;="&amp;$D$9))</f>
         <v>0</v>
       </c>
       <c r="N34" s="25" t="n">
-        <f aca="false">IF(OR(B34="",$D$8="",$D$9=""),"",SUMIFS($E$38:$E$45,$C$38:$C$45,B34,$D$38:$D$45,"Corretiva",$B$38:$B$45,"&gt;="&amp;$D$8,$B$38:$B$45,"&lt;="&amp;$D$9))</f>
+        <f aca="false">IF(OR(B34="",$D$8="",$D$9=""),"",SUMIFS($E$39:$E$46,$C$39:$C$46,B34,$D$39:$D$46,"Corretiva",$B$39:$B$46,"&gt;="&amp;$D$8,$B$39:$B$46,"&lt;="&amp;$D$9))</f>
         <v>0</v>
       </c>
-      <c r="O34" s="26" t="str">
+      <c r="O34" s="26" t="n">
         <f aca="false">IF(OR(N(K34)=0,N34=""),"",(K34-N34)/K34)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="P34" s="16" t="str">
         <f aca="false">IF(B34="","",IF(D34="","Falta o tipo",IF(F34="","Falta a criticidade",IF(AND(OR(F34="Alta",F34="Média"),G34=""),"Sem plano de preventiva",IF(L34="Atrasada","Preventiva atrasada",IF(AND(F34="Alta",J34=""),"Crítico sem contingência",IF(AND(ISNUMBER(O34),ISNUMBER($D$10)),IF(O34&lt;$D$10-0.000000001,"Disponibilidade abaixo da meta","OK"),"OK")))))))</f>
@@ -12934,461 +12940,463 @@
       </c>
       <c r="Q34" s="16"/>
     </row>
-    <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="45" t="s">
+    <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="42" t="s">
+        <v>281</v>
+      </c>
+      <c r="C35" s="38" t="s">
+        <v>372</v>
+      </c>
+      <c r="D35" s="39" t="s">
+        <v>257</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="F35" s="43" t="s">
+        <v>283</v>
+      </c>
+      <c r="G35" s="43"/>
+      <c r="H35" s="44"/>
+      <c r="I35" s="24" t="str">
+        <f aca="false">IF(OR(H35="",G35=""),"",EDATE(H35,G35))</f>
+        <v/>
+      </c>
+      <c r="J35" s="39"/>
+      <c r="K35" s="40"/>
+      <c r="L35" s="15" t="str">
+        <f aca="false">IF(B35="","",IF(G35="","Sem plano",IF(H35="","Atrasada",IF(AND(ISNUMBER($D$9),I35&lt;$D$9),"Atrasada",IF(AND(ISNUMBER($D$9),I35-$D$9&lt;=7),"Vence em 7 dias","Em dia")))))</f>
+        <v>Sem plano</v>
+      </c>
+      <c r="M35" s="14" t="n">
+        <f aca="false">IF(OR(B35="",$D$8="",$D$9=""),"",COUNTIFS($C$39:$C$46,B35,$D$39:$D$46,"Corretiva",$B$39:$B$46,"&gt;="&amp;$D$8,$B$39:$B$46,"&lt;="&amp;$D$9))</f>
+        <v>0</v>
+      </c>
+      <c r="N35" s="25" t="n">
+        <f aca="false">IF(OR(B35="",$D$8="",$D$9=""),"",SUMIFS($E$39:$E$46,$C$39:$C$46,B35,$D$39:$D$46,"Corretiva",$B$39:$B$46,"&gt;="&amp;$D$8,$B$39:$B$46,"&lt;="&amp;$D$9))</f>
+        <v>0</v>
+      </c>
+      <c r="O35" s="26" t="str">
+        <f aca="false">IF(OR(N(K35)=0,N35=""),"",(K35-N35)/K35)</f>
+        <v/>
+      </c>
+      <c r="P35" s="16" t="str">
+        <f aca="false">IF(B35="","",IF(D35="","Falta o tipo",IF(F35="","Falta a criticidade",IF(AND(OR(F35="Alta",F35="Média"),G35=""),"Sem plano de preventiva",IF(L35="Atrasada","Preventiva atrasada",IF(AND(F35="Alta",J35=""),"Crítico sem contingência",IF(AND(ISNUMBER(O35),ISNUMBER($D$10)),IF(O35&lt;$D$10-0.000000001,"Disponibilidade abaixo da meta","OK"),"OK")))))))</f>
+        <v>OK</v>
+      </c>
+      <c r="Q35" s="16"/>
+    </row>
+    <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="H36" s="45"/>
-      <c r="I36" s="45"/>
-      <c r="J36" s="45"/>
-      <c r="K36" s="45"/>
-      <c r="L36" s="45"/>
-      <c r="M36" s="45"/>
-      <c r="N36" s="45"/>
-      <c r="O36" s="45"/>
-      <c r="P36" s="45"/>
-      <c r="Q36" s="45"/>
-    </row>
-    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="13" t="s">
+      <c r="C37" s="45"/>
+      <c r="D37" s="45"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="45"/>
+      <c r="G37" s="45"/>
+      <c r="H37" s="45"/>
+      <c r="I37" s="45"/>
+      <c r="J37" s="45"/>
+      <c r="K37" s="45"/>
+      <c r="L37" s="45"/>
+      <c r="M37" s="45"/>
+      <c r="N37" s="45"/>
+      <c r="O37" s="45"/>
+      <c r="P37" s="45"/>
+      <c r="Q37" s="45"/>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C38" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="D38" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="E37" s="13" t="s">
+      <c r="E38" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="F37" s="37" t="s">
+      <c r="F38" s="37" t="s">
         <v>129</v>
       </c>
-      <c r="G37" s="37"/>
-      <c r="H37" s="37"/>
-      <c r="I37" s="37"/>
-      <c r="J37" s="13" t="s">
+      <c r="G38" s="37"/>
+      <c r="H38" s="37"/>
+      <c r="I38" s="37"/>
+      <c r="J38" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="K37" s="37" t="s">
+      <c r="K38" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="L37" s="37"/>
-      <c r="M37" s="37"/>
-      <c r="N37" s="13" t="s">
+      <c r="L38" s="37"/>
+      <c r="M38" s="37"/>
+      <c r="N38" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="O37" s="37" t="s">
+      <c r="O38" s="37" t="s">
         <v>133</v>
       </c>
-      <c r="P37" s="37"/>
-      <c r="Q37" s="13" t="s">
+      <c r="P38" s="37"/>
+      <c r="Q38" s="13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="44" t="n">
+    <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="44" t="n">
         <v>46566</v>
       </c>
-      <c r="C38" s="42" t="s">
-        <v>348</v>
-      </c>
-      <c r="D38" s="43" t="s">
+      <c r="C39" s="42" t="s">
+        <v>346</v>
+      </c>
+      <c r="D39" s="43" t="s">
         <v>139</v>
       </c>
-      <c r="E38" s="40" t="n">
+      <c r="E39" s="40" t="n">
         <v>10</v>
       </c>
-      <c r="F38" s="39" t="s">
+      <c r="F39" s="39" t="s">
         <v>373</v>
-      </c>
-      <c r="G38" s="39"/>
-      <c r="H38" s="39"/>
-      <c r="I38" s="39"/>
-      <c r="J38" s="39" t="s">
-        <v>374</v>
-      </c>
-      <c r="K38" s="39" t="s">
-        <v>375</v>
-      </c>
-      <c r="L38" s="39"/>
-      <c r="M38" s="39"/>
-      <c r="N38" s="43" t="s">
-        <v>295</v>
-      </c>
-      <c r="O38" s="39"/>
-      <c r="P38" s="39"/>
-      <c r="Q38" s="16" t="str">
-        <f aca="false">IF(C38="",IF(1&gt;0,"Falta o item",""),IF(ISNA(MATCH(C38,$B$25:$B$34,0)),"Item não cadastrado",IF(B38="","Falta a data",IF(D38="","Falta o tipo",IF(E38="","Falta o tempo parado",IF(D38="Corretiva",IF(J38="","Falta a causa",IF(K38="","Falta a ação",IF(N38="","Falta dizer se afetou o produto",IF(AND(N38="Sim",O38=""),"Produto afetado sem tratamento","OK")))),"OK"))))))</f>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="44" t="n">
-        <v>46571</v>
-      </c>
-      <c r="C39" s="42" t="s">
-        <v>366</v>
-      </c>
-      <c r="D39" s="43" t="s">
-        <v>284</v>
-      </c>
-      <c r="E39" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="39" t="s">
-        <v>376</v>
       </c>
       <c r="G39" s="39"/>
       <c r="H39" s="39"/>
       <c r="I39" s="39"/>
-      <c r="J39" s="39"/>
-      <c r="K39" s="39"/>
+      <c r="J39" s="39" t="s">
+        <v>374</v>
+      </c>
+      <c r="K39" s="39" t="s">
+        <v>375</v>
+      </c>
       <c r="L39" s="39"/>
       <c r="M39" s="39"/>
-      <c r="N39" s="43"/>
+      <c r="N39" s="43" t="s">
+        <v>295</v>
+      </c>
       <c r="O39" s="39"/>
       <c r="P39" s="39"/>
       <c r="Q39" s="16" t="str">
-        <f aca="false">IF(C39="",IF(1&gt;0,"Falta o item",""),IF(ISNA(MATCH(C39,$B$25:$B$34,0)),"Item não cadastrado",IF(B39="","Falta a data",IF(D39="","Falta o tipo",IF(E39="","Falta o tempo parado",IF(D39="Corretiva",IF(J39="","Falta a causa",IF(K39="","Falta a ação",IF(N39="","Falta dizer se afetou o produto",IF(AND(N39="Sim",O39=""),"Produto afetado sem tratamento","OK")))),"OK"))))))</f>
+        <f aca="false">IF(C39="",IF(1&gt;0,"Falta o item",""),IF(ISNA(MATCH(C39,$B$25:$B$35,0)),"Item não cadastrado",IF(B39="","Falta a data",IF(D39="","Falta o tipo",IF(E39="","Falta o tempo parado",IF(D39="Corretiva",IF(J39="","Falta a causa",IF(K39="","Falta a ação",IF(N39="","Falta dizer se afetou o produto",IF(AND(N39="Sim",O39=""),"Produto afetado sem tratamento","OK")))),"OK"))))))</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="44" t="n">
-        <v>46574</v>
+        <v>46571</v>
       </c>
       <c r="C40" s="42" t="s">
-        <v>348</v>
+        <v>366</v>
       </c>
       <c r="D40" s="43" t="s">
-        <v>139</v>
+        <v>284</v>
       </c>
       <c r="E40" s="40" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F40" s="39" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G40" s="39"/>
       <c r="H40" s="39"/>
       <c r="I40" s="39"/>
-      <c r="J40" s="39" t="s">
-        <v>378</v>
-      </c>
-      <c r="K40" s="39" t="s">
-        <v>379</v>
-      </c>
+      <c r="J40" s="39"/>
+      <c r="K40" s="39"/>
       <c r="L40" s="39"/>
       <c r="M40" s="39"/>
-      <c r="N40" s="43" t="s">
-        <v>143</v>
-      </c>
-      <c r="O40" s="39" t="s">
-        <v>380</v>
-      </c>
+      <c r="N40" s="43"/>
+      <c r="O40" s="39"/>
       <c r="P40" s="39"/>
       <c r="Q40" s="16" t="str">
-        <f aca="false">IF(C40="",IF(1&gt;0,"Falta o item",""),IF(ISNA(MATCH(C40,$B$25:$B$34,0)),"Item não cadastrado",IF(B40="","Falta a data",IF(D40="","Falta o tipo",IF(E40="","Falta o tempo parado",IF(D40="Corretiva",IF(J40="","Falta a causa",IF(K40="","Falta a ação",IF(N40="","Falta dizer se afetou o produto",IF(AND(N40="Sim",O40=""),"Produto afetado sem tratamento","OK")))),"OK"))))))</f>
+        <f aca="false">IF(C40="",IF(1&gt;0,"Falta o item",""),IF(ISNA(MATCH(C40,$B$25:$B$35,0)),"Item não cadastrado",IF(B40="","Falta a data",IF(D40="","Falta o tipo",IF(E40="","Falta o tempo parado",IF(D40="Corretiva",IF(J40="","Falta a causa",IF(K40="","Falta a ação",IF(N40="","Falta dizer se afetou o produto",IF(AND(N40="Sim",O40=""),"Produto afetado sem tratamento","OK")))),"OK"))))))</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="44" t="n">
-        <v>46580</v>
+        <v>46574</v>
       </c>
       <c r="C41" s="42" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D41" s="43" t="s">
         <v>139</v>
       </c>
       <c r="E41" s="40" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F41" s="39" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="G41" s="39"/>
       <c r="H41" s="39"/>
       <c r="I41" s="39"/>
       <c r="J41" s="39" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="K41" s="39" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="L41" s="39"/>
       <c r="M41" s="39"/>
       <c r="N41" s="43" t="s">
-        <v>295</v>
-      </c>
-      <c r="O41" s="39"/>
+        <v>143</v>
+      </c>
+      <c r="O41" s="39" t="s">
+        <v>380</v>
+      </c>
       <c r="P41" s="39"/>
       <c r="Q41" s="16" t="str">
-        <f aca="false">IF(C41="",IF(1&gt;0,"Falta o item",""),IF(ISNA(MATCH(C41,$B$25:$B$34,0)),"Item não cadastrado",IF(B41="","Falta a data",IF(D41="","Falta o tipo",IF(E41="","Falta o tempo parado",IF(D41="Corretiva",IF(J41="","Falta a causa",IF(K41="","Falta a ação",IF(N41="","Falta dizer se afetou o produto",IF(AND(N41="Sim",O41=""),"Produto afetado sem tratamento","OK")))),"OK"))))))</f>
+        <f aca="false">IF(C41="",IF(1&gt;0,"Falta o item",""),IF(ISNA(MATCH(C41,$B$25:$B$35,0)),"Item não cadastrado",IF(B41="","Falta a data",IF(D41="","Falta o tipo",IF(E41="","Falta o tempo parado",IF(D41="Corretiva",IF(J41="","Falta a causa",IF(K41="","Falta a ação",IF(N41="","Falta dizer se afetou o produto",IF(AND(N41="Sim",O41=""),"Produto afetado sem tratamento","OK")))),"OK"))))))</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="44" t="n">
-        <v>46586</v>
+        <v>46580</v>
       </c>
       <c r="C42" s="42" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D42" s="43" t="s">
         <v>139</v>
       </c>
       <c r="E42" s="40" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F42" s="39" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="G42" s="39"/>
       <c r="H42" s="39"/>
       <c r="I42" s="39"/>
       <c r="J42" s="39" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="K42" s="39" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="L42" s="39"/>
       <c r="M42" s="39"/>
       <c r="N42" s="43" t="s">
-        <v>143</v>
-      </c>
-      <c r="O42" s="39" t="s">
-        <v>387</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="O42" s="39"/>
       <c r="P42" s="39"/>
       <c r="Q42" s="16" t="str">
-        <f aca="false">IF(C42="",IF(1&gt;0,"Falta o item",""),IF(ISNA(MATCH(C42,$B$25:$B$34,0)),"Item não cadastrado",IF(B42="","Falta a data",IF(D42="","Falta o tipo",IF(E42="","Falta o tempo parado",IF(D42="Corretiva",IF(J42="","Falta a causa",IF(K42="","Falta a ação",IF(N42="","Falta dizer se afetou o produto",IF(AND(N42="Sim",O42=""),"Produto afetado sem tratamento","OK")))),"OK"))))))</f>
+        <f aca="false">IF(C42="",IF(1&gt;0,"Falta o item",""),IF(ISNA(MATCH(C42,$B$25:$B$35,0)),"Item não cadastrado",IF(B42="","Falta a data",IF(D42="","Falta o tipo",IF(E42="","Falta o tempo parado",IF(D42="Corretiva",IF(J42="","Falta a causa",IF(K42="","Falta a ação",IF(N42="","Falta dizer se afetou o produto",IF(AND(N42="Sim",O42=""),"Produto afetado sem tratamento","OK")))),"OK"))))))</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="44" t="n">
-        <v>46588</v>
+        <v>46586</v>
       </c>
       <c r="C43" s="42" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D43" s="43" t="s">
-        <v>284</v>
+        <v>139</v>
       </c>
       <c r="E43" s="40" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F43" s="39" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="G43" s="39"/>
       <c r="H43" s="39"/>
       <c r="I43" s="39"/>
-      <c r="J43" s="39"/>
-      <c r="K43" s="39"/>
+      <c r="J43" s="39" t="s">
+        <v>385</v>
+      </c>
+      <c r="K43" s="39" t="s">
+        <v>386</v>
+      </c>
       <c r="L43" s="39"/>
       <c r="M43" s="39"/>
-      <c r="N43" s="43"/>
-      <c r="O43" s="39"/>
+      <c r="N43" s="43" t="s">
+        <v>143</v>
+      </c>
+      <c r="O43" s="39" t="s">
+        <v>387</v>
+      </c>
       <c r="P43" s="39"/>
       <c r="Q43" s="16" t="str">
-        <f aca="false">IF(C43="",IF(1&gt;0,"Falta o item",""),IF(ISNA(MATCH(C43,$B$25:$B$34,0)),"Item não cadastrado",IF(B43="","Falta a data",IF(D43="","Falta o tipo",IF(E43="","Falta o tempo parado",IF(D43="Corretiva",IF(J43="","Falta a causa",IF(K43="","Falta a ação",IF(N43="","Falta dizer se afetou o produto",IF(AND(N43="Sim",O43=""),"Produto afetado sem tratamento","OK")))),"OK"))))))</f>
+        <f aca="false">IF(C43="",IF(1&gt;0,"Falta o item",""),IF(ISNA(MATCH(C43,$B$25:$B$35,0)),"Item não cadastrado",IF(B43="","Falta a data",IF(D43="","Falta o tipo",IF(E43="","Falta o tempo parado",IF(D43="Corretiva",IF(J43="","Falta a causa",IF(K43="","Falta a ação",IF(N43="","Falta dizer se afetou o produto",IF(AND(N43="Sim",O43=""),"Produto afetado sem tratamento","OK")))),"OK"))))))</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="44" t="n">
-        <v>46590</v>
+        <v>46588</v>
       </c>
       <c r="C44" s="42" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="D44" s="43" t="s">
-        <v>139</v>
+        <v>284</v>
       </c>
       <c r="E44" s="40" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F44" s="39" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G44" s="39"/>
       <c r="H44" s="39"/>
       <c r="I44" s="39"/>
-      <c r="J44" s="39" t="s">
-        <v>390</v>
-      </c>
-      <c r="K44" s="39" t="s">
-        <v>391</v>
-      </c>
+      <c r="J44" s="39"/>
+      <c r="K44" s="39"/>
       <c r="L44" s="39"/>
       <c r="M44" s="39"/>
-      <c r="N44" s="43" t="s">
-        <v>143</v>
-      </c>
+      <c r="N44" s="43"/>
       <c r="O44" s="39"/>
       <c r="P44" s="39"/>
       <c r="Q44" s="16" t="str">
-        <f aca="false">IF(C44="",IF(1&gt;0,"Falta o item",""),IF(ISNA(MATCH(C44,$B$25:$B$34,0)),"Item não cadastrado",IF(B44="","Falta a data",IF(D44="","Falta o tipo",IF(E44="","Falta o tempo parado",IF(D44="Corretiva",IF(J44="","Falta a causa",IF(K44="","Falta a ação",IF(N44="","Falta dizer se afetou o produto",IF(AND(N44="Sim",O44=""),"Produto afetado sem tratamento","OK")))),"OK"))))))</f>
-        <v>Produto afetado sem tratamento</v>
+        <f aca="false">IF(C44="",IF(1&gt;0,"Falta o item",""),IF(ISNA(MATCH(C44,$B$25:$B$35,0)),"Item não cadastrado",IF(B44="","Falta a data",IF(D44="","Falta o tipo",IF(E44="","Falta o tempo parado",IF(D44="Corretiva",IF(J44="","Falta a causa",IF(K44="","Falta a ação",IF(N44="","Falta dizer se afetou o produto",IF(AND(N44="Sim",O44=""),"Produto afetado sem tratamento","OK")))),"OK"))))))</f>
+        <v>OK</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="44" t="n">
-        <v>46595</v>
+        <v>46590</v>
       </c>
       <c r="C45" s="42" t="s">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="D45" s="43" t="s">
         <v>139</v>
       </c>
       <c r="E45" s="40" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F45" s="39" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="G45" s="39"/>
       <c r="H45" s="39"/>
       <c r="I45" s="39"/>
       <c r="J45" s="39" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="K45" s="39" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="L45" s="39"/>
       <c r="M45" s="39"/>
       <c r="N45" s="43" t="s">
-        <v>295</v>
+        <v>143</v>
       </c>
       <c r="O45" s="39"/>
       <c r="P45" s="39"/>
       <c r="Q45" s="16" t="str">
-        <f aca="false">IF(C45="",IF(1&gt;0,"Falta o item",""),IF(ISNA(MATCH(C45,$B$25:$B$34,0)),"Item não cadastrado",IF(B45="","Falta a data",IF(D45="","Falta o tipo",IF(E45="","Falta o tempo parado",IF(D45="Corretiva",IF(J45="","Falta a causa",IF(K45="","Falta a ação",IF(N45="","Falta dizer se afetou o produto",IF(AND(N45="Sim",O45=""),"Produto afetado sem tratamento","OK")))),"OK"))))))</f>
+        <f aca="false">IF(C45="",IF(1&gt;0,"Falta o item",""),IF(ISNA(MATCH(C45,$B$25:$B$35,0)),"Item não cadastrado",IF(B45="","Falta a data",IF(D45="","Falta o tipo",IF(E45="","Falta o tempo parado",IF(D45="Corretiva",IF(J45="","Falta a causa",IF(K45="","Falta a ação",IF(N45="","Falta dizer se afetou o produto",IF(AND(N45="Sim",O45=""),"Produto afetado sem tratamento","OK")))),"OK"))))))</f>
+        <v>Produto afetado sem tratamento</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B46" s="44" t="n">
+        <v>46595</v>
+      </c>
+      <c r="C46" s="42" t="s">
+        <v>346</v>
+      </c>
+      <c r="D46" s="43" t="s">
+        <v>139</v>
+      </c>
+      <c r="E46" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="F46" s="39" t="s">
+        <v>392</v>
+      </c>
+      <c r="G46" s="39"/>
+      <c r="H46" s="39"/>
+      <c r="I46" s="39"/>
+      <c r="J46" s="39" t="s">
+        <v>393</v>
+      </c>
+      <c r="K46" s="39" t="s">
+        <v>394</v>
+      </c>
+      <c r="L46" s="39"/>
+      <c r="M46" s="39"/>
+      <c r="N46" s="43" t="s">
+        <v>295</v>
+      </c>
+      <c r="O46" s="39"/>
+      <c r="P46" s="39"/>
+      <c r="Q46" s="16" t="str">
+        <f aca="false">IF(C46="",IF(1&gt;0,"Falta o item",""),IF(ISNA(MATCH(C46,$B$25:$B$35,0)),"Item não cadastrado",IF(B46="","Falta a data",IF(D46="","Falta o tipo",IF(E46="","Falta o tempo parado",IF(D46="Corretiva",IF(J46="","Falta a causa",IF(K46="","Falta a ação",IF(N46="","Falta dizer se afetou o produto",IF(AND(N46="Sim",O46=""),"Produto afetado sem tratamento","OK")))),"OK"))))))</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="46" t="s">
+    <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B48" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="C47" s="46"/>
-      <c r="D47" s="46"/>
-      <c r="E47" s="46"/>
-      <c r="F47" s="46"/>
-      <c r="G47" s="46"/>
-      <c r="H47" s="46"/>
-      <c r="I47" s="46"/>
-      <c r="J47" s="46"/>
-      <c r="K47" s="46"/>
-      <c r="L47" s="46"/>
-      <c r="M47" s="46"/>
-      <c r="N47" s="46"/>
-      <c r="O47" s="46"/>
-      <c r="P47" s="46"/>
-      <c r="Q47" s="46"/>
-    </row>
-    <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="37" t="s">
+      <c r="C48" s="46"/>
+      <c r="D48" s="46"/>
+      <c r="E48" s="46"/>
+      <c r="F48" s="46"/>
+      <c r="G48" s="46"/>
+      <c r="H48" s="46"/>
+      <c r="I48" s="46"/>
+      <c r="J48" s="46"/>
+      <c r="K48" s="46"/>
+      <c r="L48" s="46"/>
+      <c r="M48" s="46"/>
+      <c r="N48" s="46"/>
+      <c r="O48" s="46"/>
+      <c r="P48" s="46"/>
+      <c r="Q48" s="46"/>
+    </row>
+    <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B49" s="37" t="s">
         <v>150</v>
       </c>
-      <c r="C48" s="37"/>
-      <c r="D48" s="13" t="s">
+      <c r="C49" s="37"/>
+      <c r="D49" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="E48" s="13" t="s">
+      <c r="E49" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="F48" s="37" t="s">
+      <c r="F49" s="37" t="s">
         <v>151</v>
       </c>
-      <c r="G48" s="37"/>
-      <c r="H48" s="37"/>
-      <c r="I48" s="13" t="s">
+      <c r="G49" s="37"/>
+      <c r="H49" s="37"/>
+      <c r="I49" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="J48" s="13" t="s">
+      <c r="J49" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="K48" s="13" t="s">
+      <c r="K49" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="L48" s="13" t="s">
+      <c r="L49" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="M48" s="13" t="s">
+      <c r="M49" s="13" t="s">
         <v>301</v>
       </c>
-      <c r="N48" s="13" t="s">
+      <c r="N49" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="O48" s="37" t="s">
+      <c r="O49" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="P48" s="37"/>
-      <c r="Q48" s="13" t="s">
+      <c r="P49" s="37"/>
+      <c r="Q49" s="13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="38" t="s">
+    <row r="50" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B50" s="38" t="s">
         <v>395</v>
-      </c>
-      <c r="C49" s="38"/>
-      <c r="D49" s="43" t="s">
-        <v>162</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="F49" s="39" t="s">
-        <v>396</v>
-      </c>
-      <c r="G49" s="39"/>
-      <c r="H49" s="39"/>
-      <c r="I49" s="47" t="s">
-        <v>165</v>
-      </c>
-      <c r="J49" s="39" t="s">
-        <v>397</v>
-      </c>
-      <c r="K49" s="40" t="n">
-        <v>18</v>
-      </c>
-      <c r="L49" s="40" t="n">
-        <v>28</v>
-      </c>
-      <c r="M49" s="40" t="n">
-        <v>31</v>
-      </c>
-      <c r="N49" s="15" t="str">
-        <f aca="false">IF(B49="","",IF(M49="","Sem medição",IF(OR(AND(K49&lt;&gt;"",M49&lt;K49),AND(L49&lt;&gt;"",M49&gt;L49)),"Fora","Dentro")))</f>
-        <v>Fora</v>
-      </c>
-      <c r="O49" s="39" t="s">
-        <v>398</v>
-      </c>
-      <c r="P49" s="39"/>
-      <c r="Q49" s="16" t="str">
-        <f aca="false">IF(B49="","",IF(F49="","Falta por que afeta o produto",IF(J49="","Falta como é controlado",IF(AND(K49="",L49=""),"Falta o limite",IF(N49="Sem medição","Falta a medição",IF(AND(N49="Fora",O49=""),"Fora do limite: falta a ação","OK"))))))</f>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="38" t="s">
-        <v>399</v>
       </c>
       <c r="C50" s="38"/>
       <c r="D50" s="43" t="s">
@@ -13398,112 +13406,116 @@
         <v>353</v>
       </c>
       <c r="F50" s="39" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="G50" s="39"/>
       <c r="H50" s="39"/>
       <c r="I50" s="47" t="s">
-        <v>401</v>
+        <v>165</v>
       </c>
       <c r="J50" s="39" t="s">
         <v>397</v>
       </c>
       <c r="K50" s="40" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="L50" s="40" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="M50" s="40" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="N50" s="15" t="str">
         <f aca="false">IF(B50="","",IF(M50="","Sem medição",IF(OR(AND(K50&lt;&gt;"",M50&lt;K50),AND(L50&lt;&gt;"",M50&gt;L50)),"Fora","Dentro")))</f>
-        <v>Dentro</v>
-      </c>
-      <c r="O50" s="39"/>
+        <v>Fora</v>
+      </c>
+      <c r="O50" s="39" t="s">
+        <v>398</v>
+      </c>
       <c r="P50" s="39"/>
       <c r="Q50" s="16" t="str">
         <f aca="false">IF(B50="","",IF(F50="","Falta por que afeta o produto",IF(J50="","Falta como é controlado",IF(AND(K50="",L50=""),"Falta o limite",IF(N50="Sem medição","Falta a medição",IF(AND(N50="Fora",O50=""),"Fora do limite: falta a ação","OK"))))))</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="38" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C51" s="38"/>
       <c r="D51" s="43" t="s">
         <v>162</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="F51" s="39" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="G51" s="39"/>
       <c r="H51" s="39"/>
       <c r="I51" s="47" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="J51" s="39" t="s">
-        <v>405</v>
-      </c>
-      <c r="K51" s="40"/>
+        <v>397</v>
+      </c>
+      <c r="K51" s="40" t="n">
+        <v>40</v>
+      </c>
       <c r="L51" s="40" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="M51" s="40" t="n">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="N51" s="15" t="str">
         <f aca="false">IF(B51="","",IF(M51="","Sem medição",IF(OR(AND(K51&lt;&gt;"",M51&lt;K51),AND(L51&lt;&gt;"",M51&gt;L51)),"Fora","Dentro")))</f>
-        <v>Fora</v>
-      </c>
-      <c r="O51" s="39" t="s">
-        <v>406</v>
-      </c>
+        <v>Dentro</v>
+      </c>
+      <c r="O51" s="39"/>
       <c r="P51" s="39"/>
       <c r="Q51" s="16" t="str">
         <f aca="false">IF(B51="","",IF(F51="","Falta por que afeta o produto",IF(J51="","Falta como é controlado",IF(AND(K51="",L51=""),"Falta o limite",IF(N51="Sem medição","Falta a medição",IF(AND(N51="Fora",O51=""),"Fora do limite: falta a ação","OK"))))))</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="38" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="C52" s="38"/>
       <c r="D52" s="43" t="s">
         <v>162</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="F52" s="39" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="G52" s="39"/>
       <c r="H52" s="39"/>
       <c r="I52" s="47" t="s">
-        <v>310</v>
+        <v>404</v>
       </c>
       <c r="J52" s="39" t="s">
-        <v>409</v>
-      </c>
-      <c r="K52" s="40" t="n">
-        <v>95</v>
-      </c>
-      <c r="L52" s="40"/>
+        <v>405</v>
+      </c>
+      <c r="K52" s="40"/>
+      <c r="L52" s="40" t="n">
+        <v>85</v>
+      </c>
       <c r="M52" s="40" t="n">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="N52" s="15" t="str">
         <f aca="false">IF(B52="","",IF(M52="","Sem medição",IF(OR(AND(K52&lt;&gt;"",M52&lt;K52),AND(L52&lt;&gt;"",M52&gt;L52)),"Fora","Dentro")))</f>
-        <v>Dentro</v>
-      </c>
-      <c r="O52" s="39"/>
+        <v>Fora</v>
+      </c>
+      <c r="O52" s="39" t="s">
+        <v>406</v>
+      </c>
       <c r="P52" s="39"/>
       <c r="Q52" s="16" t="str">
         <f aca="false">IF(B52="","",IF(F52="","Falta por que afeta o produto",IF(J52="","Falta como é controlado",IF(AND(K52="",L52=""),"Falta o limite",IF(N52="Sem medição","Falta a medição",IF(AND(N52="Fora",O52=""),"Fora do limite: falta a ação","OK"))))))</f>
@@ -13512,134 +13524,151 @@
     </row>
     <row r="53" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="38" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C53" s="38"/>
       <c r="D53" s="43" t="s">
-        <v>323</v>
+        <v>162</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>336</v>
+        <v>357</v>
       </c>
       <c r="F53" s="39" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G53" s="39"/>
       <c r="H53" s="39"/>
       <c r="I53" s="47" t="s">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="J53" s="39" t="s">
-        <v>412</v>
-      </c>
-      <c r="K53" s="40"/>
-      <c r="L53" s="40" t="n">
-        <v>16</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="K53" s="40" t="n">
+        <v>95</v>
+      </c>
+      <c r="L53" s="40"/>
       <c r="M53" s="40" t="n">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="N53" s="15" t="str">
         <f aca="false">IF(B53="","",IF(M53="","Sem medição",IF(OR(AND(K53&lt;&gt;"",M53&lt;K53),AND(L53&lt;&gt;"",M53&gt;L53)),"Fora","Dentro")))</f>
-        <v>Fora</v>
+        <v>Dentro</v>
       </c>
       <c r="O53" s="39"/>
       <c r="P53" s="39"/>
       <c r="Q53" s="16" t="str">
         <f aca="false">IF(B53="","",IF(F53="","Falta por que afeta o produto",IF(J53="","Falta como é controlado",IF(AND(K53="",L53=""),"Falta o limite",IF(N53="Sem medição","Falta a medição",IF(AND(N53="Fora",O53=""),"Fora do limite: falta a ação","OK"))))))</f>
-        <v>Fora do limite: falta a ação</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="38" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C54" s="38"/>
       <c r="D54" s="43" t="s">
         <v>317</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F54" s="39" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="G54" s="39"/>
       <c r="H54" s="39"/>
       <c r="I54" s="47" t="s">
-        <v>415</v>
+        <v>324</v>
       </c>
       <c r="J54" s="39" t="s">
-        <v>416</v>
-      </c>
-      <c r="K54" s="40" t="n">
-        <v>90</v>
-      </c>
-      <c r="L54" s="40"/>
-      <c r="M54" s="40"/>
+        <v>412</v>
+      </c>
+      <c r="K54" s="40"/>
+      <c r="L54" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="M54" s="40" t="n">
+        <v>22</v>
+      </c>
       <c r="N54" s="15" t="str">
         <f aca="false">IF(B54="","",IF(M54="","Sem medição",IF(OR(AND(K54&lt;&gt;"",M54&lt;K54),AND(L54&lt;&gt;"",M54&gt;L54)),"Fora","Dentro")))</f>
-        <v>Sem medição</v>
+        <v>Fora</v>
       </c>
       <c r="O54" s="39"/>
       <c r="P54" s="39"/>
       <c r="Q54" s="16" t="str">
         <f aca="false">IF(B54="","",IF(F54="","Falta por que afeta o produto",IF(J54="","Falta como é controlado",IF(AND(K54="",L54=""),"Falta o limite",IF(N54="Sem medição","Falta a medição",IF(AND(N54="Fora",O54=""),"Fora do limite: falta a ação","OK"))))))</f>
+        <v>Fora do limite: falta a ação</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B55" s="38" t="s">
+        <v>413</v>
+      </c>
+      <c r="C55" s="38"/>
+      <c r="D55" s="43" t="s">
+        <v>317</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="F55" s="39" t="s">
+        <v>414</v>
+      </c>
+      <c r="G55" s="39"/>
+      <c r="H55" s="39"/>
+      <c r="I55" s="47" t="s">
+        <v>415</v>
+      </c>
+      <c r="J55" s="39" t="s">
+        <v>416</v>
+      </c>
+      <c r="K55" s="40" t="n">
+        <v>90</v>
+      </c>
+      <c r="L55" s="40"/>
+      <c r="M55" s="40"/>
+      <c r="N55" s="15" t="str">
+        <f aca="false">IF(B55="","",IF(M55="","Sem medição",IF(OR(AND(K55&lt;&gt;"",M55&lt;K55),AND(L55&lt;&gt;"",M55&gt;L55)),"Fora","Dentro")))</f>
+        <v>Sem medição</v>
+      </c>
+      <c r="O55" s="39"/>
+      <c r="P55" s="39"/>
+      <c r="Q55" s="16" t="str">
+        <f aca="false">IF(B55="","",IF(F55="","Falta por que afeta o produto",IF(J55="","Falta como é controlado",IF(AND(K55="",L55=""),"Falta o limite",IF(N55="Sem medição","Falta a medição",IF(AND(N55="Fora",O55=""),"Fora do limite: falta a ação","OK"))))))</f>
         <v>Falta a medição</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B56" s="17" t="s">
+    <row r="57" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B57" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C56" s="17"/>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="17"/>
-      <c r="G56" s="17"/>
-      <c r="H56" s="17"/>
-      <c r="I56" s="17"/>
-      <c r="J56" s="17"/>
-      <c r="K56" s="17"/>
-      <c r="L56" s="17"/>
-      <c r="M56" s="17"/>
-      <c r="N56" s="17"/>
-      <c r="O56" s="17"/>
-      <c r="P56" s="17"/>
-      <c r="Q56" s="17"/>
-    </row>
-    <row r="57" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B57" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="C57" s="18"/>
-      <c r="D57" s="18"/>
-      <c r="E57" s="19" t="str">
-        <f aca="false">COUNTIF(L14:L21,"Falta gente")&amp;" funções com falta de gente, "&amp;-SUMIF(K14:K21,"&lt;0")&amp;" pessoas a menos no pico, "&amp;COUNTIF(M14:M21,"Sem pessoa qualificada na escala")&amp;" sem pessoa qualificada"</f>
-        <v>2 funções com falta de gente, 2 pessoas a menos no pico, 0 sem pessoa qualificada</v>
-      </c>
-      <c r="F57" s="19"/>
-      <c r="G57" s="19"/>
-      <c r="H57" s="19"/>
-      <c r="I57" s="19"/>
-      <c r="J57" s="19"/>
-      <c r="K57" s="19"/>
-      <c r="L57" s="19"/>
-      <c r="M57" s="19"/>
-      <c r="N57" s="19"/>
-      <c r="O57" s="19"/>
-      <c r="P57" s="19"/>
-      <c r="Q57" s="19"/>
+      <c r="C57" s="17"/>
+      <c r="D57" s="17"/>
+      <c r="E57" s="17"/>
+      <c r="F57" s="17"/>
+      <c r="G57" s="17"/>
+      <c r="H57" s="17"/>
+      <c r="I57" s="17"/>
+      <c r="J57" s="17"/>
+      <c r="K57" s="17"/>
+      <c r="L57" s="17"/>
+      <c r="M57" s="17"/>
+      <c r="N57" s="17"/>
+      <c r="O57" s="17"/>
+      <c r="P57" s="17"/>
+      <c r="Q57" s="17"/>
     </row>
     <row r="58" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="18" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="C58" s="18"/>
       <c r="D58" s="18"/>
       <c r="E58" s="19" t="str">
-        <f aca="false">COUNTIF(L25:L34,"Em dia")&amp;" em dia"&amp;", "&amp;COUNTIF(L25:L34,"Vence em 7 dias")&amp;" vence em 7 dias"&amp;", "&amp;COUNTIF(L25:L34,"Atrasada")&amp;" atrasada"&amp;", "&amp;COUNTIF(L25:L34,"Sem plano")&amp;" sem plano"</f>
-        <v>7 em dia, 1 vence em 7 dias, 1 atrasada, 1 sem plano</v>
+        <f aca="false">COUNTIF(L14:L21,"Falta gente")&amp;" funções com falta de gente, "&amp;-SUMIF(K14:K21,"&lt;0")&amp;" pessoas a menos no pico, "&amp;COUNTIF(M14:M21,"Sem pessoa qualificada na escala")&amp;" sem pessoa qualificada"</f>
+        <v>2 funções com falta de gente, 2 pessoas a menos no pico, 0 sem pessoa qualificada</v>
       </c>
       <c r="F58" s="19"/>
       <c r="G58" s="19"/>
@@ -13656,13 +13685,13 @@
     </row>
     <row r="59" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="18" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C59" s="18"/>
       <c r="D59" s="18"/>
       <c r="E59" s="19" t="str">
-        <f aca="false">SUM(M25:M34)&amp;" corretivas, "&amp;SUM(N25:N34)&amp;" horas paradas, "&amp;COUNTIF(O25:O34,"&lt;"&amp;($D$10-0.000000001))&amp;" item abaixo da meta"</f>
-        <v>5 corretivas, 52 horas paradas, 1 item abaixo da meta</v>
+        <f aca="false">COUNTIF(L25:L35,"Em dia")&amp;" em dia"&amp;", "&amp;COUNTIF(L25:L35,"Vence em 7 dias")&amp;" vence em 7 dias"&amp;", "&amp;COUNTIF(L25:L35,"Atrasada")&amp;" atrasada"&amp;", "&amp;COUNTIF(L25:L35,"Sem plano")&amp;" sem plano"</f>
+        <v>8 em dia, 1 vence em 7 dias, 1 atrasada, 1 sem plano</v>
       </c>
       <c r="F59" s="19"/>
       <c r="G59" s="19"/>
@@ -13679,13 +13708,13 @@
     </row>
     <row r="60" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="18" t="s">
-        <v>32</v>
+        <v>127</v>
       </c>
       <c r="C60" s="18"/>
       <c r="D60" s="18"/>
       <c r="E60" s="19" t="str">
-        <f aca="false">COUNTIF(N49:N54,"Dentro")&amp;" dentro"&amp;", "&amp;COUNTIF(N49:N54,"Fora")&amp;" fora"&amp;", "&amp;COUNTIF(N49:N54,"Sem medição")&amp;" sem medição"</f>
-        <v>2 dentro, 3 fora, 1 sem medição</v>
+        <f aca="false">SUM(M25:M35)&amp;" corretivas, "&amp;SUM(N25:N35)&amp;" horas paradas, "&amp;COUNTIF(O25:O35,"&lt;"&amp;($D$10-0.000000001))&amp;" item abaixo da meta"</f>
+        <v>5 corretivas, 52 horas paradas, 1 item abaixo da meta</v>
       </c>
       <c r="F60" s="19"/>
       <c r="G60" s="19"/>
@@ -13702,13 +13731,13 @@
     </row>
     <row r="61" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="18" t="s">
-        <v>207</v>
+        <v>32</v>
       </c>
       <c r="C61" s="18"/>
       <c r="D61" s="18"/>
-      <c r="E61" s="19" t="n">
-        <f aca="false">SUMPRODUCT((M14:M21&lt;&gt;"OK")*1)+SUMPRODUCT((P25:P34&lt;&gt;"OK")*1)+SUMPRODUCT((Q38:Q45&lt;&gt;"OK")*1)+SUMPRODUCT((Q49:Q54&lt;&gt;"OK")*1)</f>
-        <v>7</v>
+      <c r="E61" s="19" t="str">
+        <f aca="false">COUNTIF(N50:N55,"Dentro")&amp;" dentro"&amp;", "&amp;COUNTIF(N50:N55,"Fora")&amp;" fora"&amp;", "&amp;COUNTIF(N50:N55,"Sem medição")&amp;" sem medição"</f>
+        <v>2 dentro, 3 fora, 1 sem medição</v>
       </c>
       <c r="F61" s="19"/>
       <c r="G61" s="19"/>
@@ -13723,8 +13752,31 @@
       <c r="P61" s="19"/>
       <c r="Q61" s="19"/>
     </row>
+    <row r="62" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B62" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="C62" s="18"/>
+      <c r="D62" s="18"/>
+      <c r="E62" s="19" t="n">
+        <f aca="false">SUMPRODUCT((M14:M21&lt;&gt;"OK")*1)+SUMPRODUCT((P25:P35&lt;&gt;"OK")*1)+SUMPRODUCT((Q39:Q46&lt;&gt;"OK")*1)+SUMPRODUCT((Q50:Q55&lt;&gt;"OK")*1)</f>
+        <v>7</v>
+      </c>
+      <c r="F62" s="19"/>
+      <c r="G62" s="19"/>
+      <c r="H62" s="19"/>
+      <c r="I62" s="19"/>
+      <c r="J62" s="19"/>
+      <c r="K62" s="19"/>
+      <c r="L62" s="19"/>
+      <c r="M62" s="19"/>
+      <c r="N62" s="19"/>
+      <c r="O62" s="19"/>
+      <c r="P62" s="19"/>
+      <c r="Q62" s="19"/>
+    </row>
   </sheetData>
-  <mergeCells count="105">
+  <mergeCells count="106">
     <mergeCell ref="B1:Q1"/>
     <mergeCell ref="B2:Q2"/>
     <mergeCell ref="B4:C4"/>
@@ -13769,10 +13821,8 @@
     <mergeCell ref="P32:Q32"/>
     <mergeCell ref="P33:Q33"/>
     <mergeCell ref="P34:Q34"/>
-    <mergeCell ref="B36:Q36"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="K37:M37"/>
-    <mergeCell ref="O37:P37"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="B37:Q37"/>
     <mergeCell ref="F38:I38"/>
     <mergeCell ref="K38:M38"/>
     <mergeCell ref="O38:P38"/>
@@ -13797,10 +13847,10 @@
     <mergeCell ref="F45:I45"/>
     <mergeCell ref="K45:M45"/>
     <mergeCell ref="O45:P45"/>
-    <mergeCell ref="B47:Q47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="O48:P48"/>
+    <mergeCell ref="F46:I46"/>
+    <mergeCell ref="K46:M46"/>
+    <mergeCell ref="O46:P46"/>
+    <mergeCell ref="B48:Q48"/>
     <mergeCell ref="B49:C49"/>
     <mergeCell ref="F49:H49"/>
     <mergeCell ref="O49:P49"/>
@@ -13819,9 +13869,10 @@
     <mergeCell ref="B54:C54"/>
     <mergeCell ref="F54:H54"/>
     <mergeCell ref="O54:P54"/>
-    <mergeCell ref="B56:Q56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="E57:Q57"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="O55:P55"/>
+    <mergeCell ref="B57:Q57"/>
     <mergeCell ref="B58:D58"/>
     <mergeCell ref="E58:Q58"/>
     <mergeCell ref="B59:D59"/>
@@ -13830,6 +13881,8 @@
     <mergeCell ref="E60:Q60"/>
     <mergeCell ref="B61:D61"/>
     <mergeCell ref="E61:Q61"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="E62:Q62"/>
   </mergeCells>
   <conditionalFormatting sqref="L14:L21">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -13850,7 +13903,7 @@
       <formula>AND(LEN($M14)&gt;0,NOT(OR($M14="OK")))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L25:L34">
+  <conditionalFormatting sqref="L25:L35">
     <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>L25="Em dia"</formula>
     </cfRule>
@@ -13864,12 +13917,12 @@
       <formula>L25="Sem plano"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O25:O34">
+  <conditionalFormatting sqref="O25:O35">
     <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(O25),O25&lt;$D$10-0.000000001)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P25:Q34">
+  <conditionalFormatting sqref="P25:Q35">
     <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>OR($P25="OK")</formula>
     </cfRule>
@@ -13877,37 +13930,37 @@
       <formula>AND(LEN($P25)&gt;0,NOT(OR($P25="OK")))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q38:Q45">
+  <conditionalFormatting sqref="Q39:Q46">
     <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>Q38="OK"</formula>
+      <formula>Q39="OK"</formula>
     </cfRule>
     <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>Q38="Produto afetado sem tratamento"</formula>
+      <formula>Q39="Produto afetado sem tratamento"</formula>
     </cfRule>
     <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
-      <formula>LEN(Q38)&gt;0</formula>
+      <formula>LEN(Q39)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N49:N54">
+  <conditionalFormatting sqref="N50:N55">
     <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>N49="Dentro"</formula>
+      <formula>N50="Dentro"</formula>
     </cfRule>
     <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>N49="Fora"</formula>
+      <formula>N50="Fora"</formula>
     </cfRule>
     <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>N49="Sem medição"</formula>
+      <formula>N50="Sem medição"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q49:Q54">
+  <conditionalFormatting sqref="Q50:Q55">
     <cfRule type="expression" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>Q49="OK"</formula>
+      <formula>Q50="OK"</formula>
     </cfRule>
     <cfRule type="expression" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>Q49="Fora do limite: falta a ação"</formula>
+      <formula>Q50="Fora do limite: falta a ação"</formula>
     </cfRule>
     <cfRule type="expression" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
-      <formula>LEN(Q49)&gt;0</formula>
+      <formula>LEN(Q50)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
@@ -13918,7 +13971,7 @@
     <oddFooter/>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="35" man="true" max="16383" min="0"/>
+    <brk id="36" man="true" max="16383" min="0"/>
   </rowBreaks>
 </worksheet>
 </file>
--- a/Recursos/Recursos-modelo.xlsx
+++ b/Recursos/Recursos-modelo.xlsx
@@ -2094,11 +2094,11 @@
         </c:ser>
         <c:gapWidth val="70"/>
         <c:overlap val="0"/>
-        <c:axId val="72058169"/>
-        <c:axId val="12351476"/>
+        <c:axId val="54327391"/>
+        <c:axId val="15477548"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="72058169"/>
+        <c:axId val="54327391"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2130,7 +2130,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12351476"/>
+        <c:crossAx val="15477548"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2138,7 +2138,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="12351476"/>
+        <c:axId val="15477548"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2178,7 +2178,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="72058169"/>
+        <c:crossAx val="54327391"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
